--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3680-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3680-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32DD7D33-E1BC-4BD2-99D3-A0D74C66AEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DAB8D5B-08F3-4282-97A2-9CDDE20997D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{EB287C7F-542F-4199-8C60-D5FBBE6347C3}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{ACD940B5-8976-4642-8601-A871DCF373EF}"/>
   </bookViews>
   <sheets>
     <sheet name="3680-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1499,25 +1499,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A23568-C420-4CD3-831B-387CADF545AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7743DE9E-54C5-4B4C-8CFA-7092D1398654}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1545,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1575,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1671,7 +1671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2021</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2020</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2019</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2018</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2017</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2016</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2015</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2014</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2013</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2012</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2011</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2010</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2009</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39" t="s">
         <v>52</v>
       </c>
